--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N7_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N7_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>72.27220048662056</v>
+        <v>11.74423257907584</v>
       </c>
       <c r="D2" t="n">
-        <v>74.5576227310813</v>
+        <v>12.11561369380071</v>
       </c>
       <c r="E2" t="n">
-        <v>20.08830867456853</v>
+        <v>3.264350159617386</v>
       </c>
       <c r="F2" t="n">
-        <v>21.14302629468702</v>
+        <v>3.435741772886641</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>79.48954200133704</v>
+        <v>12.91705057521727</v>
       </c>
       <c r="D3" t="n">
-        <v>82.14931537945195</v>
+        <v>13.34926374916094</v>
       </c>
       <c r="E3" t="n">
-        <v>20.08830867456853</v>
+        <v>3.264350159617386</v>
       </c>
       <c r="F3" t="n">
-        <v>21.14302629468702</v>
+        <v>3.435741772886641</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>36.70816058417341</v>
+        <v>5.965076094928179</v>
       </c>
       <c r="D4" t="n">
-        <v>36.86633575524074</v>
+        <v>5.990779560226621</v>
       </c>
       <c r="E4" t="n">
-        <v>20.08830867456853</v>
+        <v>3.264350159617386</v>
       </c>
       <c r="F4" t="n">
-        <v>21.14302629468702</v>
+        <v>3.435741772886641</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>36.64166445180493</v>
+        <v>5.954270473418301</v>
       </c>
       <c r="D5" t="n">
-        <v>36.79810486345663</v>
+        <v>5.979692040311702</v>
       </c>
       <c r="E5" t="n">
-        <v>20.08830867456853</v>
+        <v>3.264350159617386</v>
       </c>
       <c r="F5" t="n">
-        <v>21.14302629468702</v>
+        <v>3.435741772886641</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>23.54758882118923</v>
+        <v>3.82648318344325</v>
       </c>
       <c r="D6" t="n">
-        <v>23.57939049128476</v>
+        <v>3.831650954833773</v>
       </c>
       <c r="E6" t="n">
-        <v>20.08830867456853</v>
+        <v>3.264350159617386</v>
       </c>
       <c r="F6" t="n">
-        <v>21.14302629468702</v>
+        <v>3.435741772886641</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>48.59961470432066</v>
+        <v>7.897437389452107</v>
       </c>
       <c r="D7" t="n">
-        <v>48.65474134013337</v>
+        <v>7.906395467771673</v>
       </c>
       <c r="E7" t="n">
-        <v>20.08830867456853</v>
+        <v>3.264350159617386</v>
       </c>
       <c r="F7" t="n">
-        <v>21.14302629468702</v>
+        <v>3.435741772886641</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
